--- a/tables/table-1-dataset-composition-summary.xlsx
+++ b/tables/table-1-dataset-composition-summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE5FE223-C715-4D1A-89B2-682C6F148879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{BE5FE223-C715-4D1A-89B2-682C6F148879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7667098-4A76-4327-83B8-A66CD4B14883}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEF35837-4A4C-4083-9306-071224EDE2D9}"/>
   </bookViews>
@@ -202,20 +202,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -231,64 +224,26 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -304,37 +259,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
     <dxf>
       <font>
         <strike val="0"/>
@@ -348,7 +295,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -363,7 +310,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -378,7 +325,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -393,18 +340,43 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
           <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -420,19 +392,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -447,47 +407,13 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -503,8 +429,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{67F94758-29E0-44CA-8C44-5CC6F502A33F}" name="Table3" displayName="Table3" ref="A2:F53" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A2:F53" xr:uid="{67F94758-29E0-44CA-8C44-5CC6F502A33F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{67F94758-29E0-44CA-8C44-5CC6F502A33F}" name="Table3" displayName="Table3" ref="A2:F53" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowBorderDxfId="6">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{42EFBD22-B294-4763-9994-E6D9809803A3}" name="ID" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{D1997DF4-EADF-4764-AA20-0291CAA85463}" name="Species Name" dataDxfId="4"/>
@@ -814,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F378C6-F5C9-4D58-92A2-671933BE0497}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -824,1048 +749,1050 @@
     <col min="6" max="6" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>140</v>
       </c>
-      <c r="D3" s="3">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="D3" s="5">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>129</v>
       </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>5</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>136</v>
       </c>
-      <c r="D5" s="3">
-        <v>5</v>
-      </c>
-      <c r="E5" s="3">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="D5" s="5">
+        <v>5</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5">
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>133</v>
       </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>134</v>
       </c>
-      <c r="D7" s="3">
-        <v>5</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="D7" s="5">
+        <v>5</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>177</v>
       </c>
-      <c r="D8" s="3">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="D8" s="5">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5">
         <v>187</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>117</v>
       </c>
-      <c r="D9" s="3">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>5</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="D9" s="5">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5">
         <v>127</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>121</v>
       </c>
-      <c r="D10" s="3">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>131</v>
       </c>
-      <c r="D11" s="3">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>5</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="D11" s="5">
+        <v>5</v>
+      </c>
+      <c r="E11" s="5">
+        <v>5</v>
+      </c>
+      <c r="F11" s="5">
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>122</v>
       </c>
-      <c r="D12" s="3">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="D12" s="5">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5">
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>105</v>
       </c>
-      <c r="D13" s="3">
-        <v>5</v>
-      </c>
-      <c r="E13" s="3">
-        <v>5</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="D13" s="5">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>169</v>
       </c>
-      <c r="D14" s="3">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>5</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="D14" s="5">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5">
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>160</v>
       </c>
-      <c r="D15" s="3">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="D15" s="5">
+        <v>5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5">
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>136</v>
       </c>
-      <c r="D16" s="3">
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
-        <v>5</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="D16" s="5">
+        <v>5</v>
+      </c>
+      <c r="E16" s="5">
+        <v>5</v>
+      </c>
+      <c r="F16" s="5">
         <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>142</v>
       </c>
-      <c r="D17" s="3">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
         <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>165</v>
       </c>
-      <c r="D18" s="3">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="D18" s="5">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5">
+        <v>5</v>
+      </c>
+      <c r="F18" s="5">
         <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>139</v>
       </c>
-      <c r="D19" s="3">
-        <v>5</v>
-      </c>
-      <c r="E19" s="3">
-        <v>5</v>
-      </c>
-      <c r="F19" s="4">
+      <c r="D19" s="5">
+        <v>5</v>
+      </c>
+      <c r="E19" s="5">
+        <v>5</v>
+      </c>
+      <c r="F19" s="5">
         <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>131</v>
       </c>
-      <c r="D20" s="3">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5</v>
-      </c>
-      <c r="F20" s="4">
+      <c r="D20" s="5">
+        <v>5</v>
+      </c>
+      <c r="E20" s="5">
+        <v>5</v>
+      </c>
+      <c r="F20" s="5">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="5">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>137</v>
       </c>
-      <c r="D21" s="3">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3">
-        <v>5</v>
-      </c>
-      <c r="F21" s="4">
+      <c r="D21" s="5">
+        <v>5</v>
+      </c>
+      <c r="E21" s="5">
+        <v>5</v>
+      </c>
+      <c r="F21" s="5">
         <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="5">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>120</v>
       </c>
-      <c r="D22" s="3">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>5</v>
-      </c>
-      <c r="F22" s="4">
+      <c r="D22" s="5">
+        <v>5</v>
+      </c>
+      <c r="E22" s="5">
+        <v>5</v>
+      </c>
+      <c r="F22" s="5">
         <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="5">
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>143</v>
       </c>
-      <c r="D23" s="3">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>5</v>
-      </c>
-      <c r="F23" s="4">
+      <c r="D23" s="5">
+        <v>5</v>
+      </c>
+      <c r="E23" s="5">
+        <v>5</v>
+      </c>
+      <c r="F23" s="5">
         <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>120</v>
       </c>
-      <c r="D24" s="3">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>5</v>
-      </c>
-      <c r="F24" s="4">
+      <c r="D24" s="5">
+        <v>5</v>
+      </c>
+      <c r="E24" s="5">
+        <v>5</v>
+      </c>
+      <c r="F24" s="5">
         <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="5">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>186</v>
       </c>
-      <c r="D25" s="3">
-        <v>5</v>
-      </c>
-      <c r="E25" s="3">
-        <v>5</v>
-      </c>
-      <c r="F25" s="4">
+      <c r="D25" s="5">
+        <v>5</v>
+      </c>
+      <c r="E25" s="5">
+        <v>5</v>
+      </c>
+      <c r="F25" s="5">
         <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>175</v>
       </c>
-      <c r="D26" s="3">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>5</v>
-      </c>
-      <c r="F26" s="4">
+      <c r="D26" s="5">
+        <v>5</v>
+      </c>
+      <c r="E26" s="5">
+        <v>5</v>
+      </c>
+      <c r="F26" s="5">
         <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>175</v>
       </c>
-      <c r="D27" s="3">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>5</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="D27" s="5">
+        <v>5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>5</v>
+      </c>
+      <c r="F27" s="5">
         <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>167</v>
       </c>
-      <c r="D28" s="3">
-        <v>5</v>
-      </c>
-      <c r="E28" s="3">
-        <v>5</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="D28" s="5">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>5</v>
+      </c>
+      <c r="F28" s="5">
         <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>117</v>
       </c>
-      <c r="D29" s="3">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3">
-        <v>5</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="D29" s="5">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5">
+        <v>5</v>
+      </c>
+      <c r="F29" s="5">
         <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>123</v>
       </c>
-      <c r="D30" s="3">
-        <v>5</v>
-      </c>
-      <c r="E30" s="3">
-        <v>5</v>
-      </c>
-      <c r="F30" s="4">
+      <c r="D30" s="5">
+        <v>5</v>
+      </c>
+      <c r="E30" s="5">
+        <v>5</v>
+      </c>
+      <c r="F30" s="5">
         <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="5">
         <v>29</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>170</v>
       </c>
-      <c r="D31" s="3">
-        <v>5</v>
-      </c>
-      <c r="E31" s="3">
-        <v>5</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="D31" s="5">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5">
+        <v>5</v>
+      </c>
+      <c r="F31" s="5">
         <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="5">
         <v>30</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>168</v>
       </c>
-      <c r="D32" s="3">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>5</v>
-      </c>
-      <c r="F32" s="4">
+      <c r="D32" s="5">
+        <v>5</v>
+      </c>
+      <c r="E32" s="5">
+        <v>5</v>
+      </c>
+      <c r="F32" s="5">
         <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="5">
         <v>31</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>132</v>
       </c>
-      <c r="D33" s="3">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>5</v>
-      </c>
-      <c r="F33" s="4">
+      <c r="D33" s="5">
+        <v>5</v>
+      </c>
+      <c r="E33" s="5">
+        <v>5</v>
+      </c>
+      <c r="F33" s="5">
         <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="5">
         <v>32</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>121</v>
       </c>
-      <c r="D34" s="3">
-        <v>5</v>
-      </c>
-      <c r="E34" s="3">
-        <v>5</v>
-      </c>
-      <c r="F34" s="4">
+      <c r="D34" s="5">
+        <v>5</v>
+      </c>
+      <c r="E34" s="5">
+        <v>5</v>
+      </c>
+      <c r="F34" s="5">
         <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="5">
         <v>33</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>174</v>
       </c>
-      <c r="D35" s="3">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>5</v>
-      </c>
-      <c r="F35" s="4">
+      <c r="D35" s="5">
+        <v>5</v>
+      </c>
+      <c r="E35" s="5">
+        <v>5</v>
+      </c>
+      <c r="F35" s="5">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="5">
         <v>34</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>149</v>
       </c>
-      <c r="D36" s="3">
-        <v>5</v>
-      </c>
-      <c r="E36" s="3">
-        <v>5</v>
-      </c>
-      <c r="F36" s="4">
+      <c r="D36" s="5">
+        <v>5</v>
+      </c>
+      <c r="E36" s="5">
+        <v>5</v>
+      </c>
+      <c r="F36" s="5">
         <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="5">
         <v>35</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>170</v>
       </c>
-      <c r="D37" s="3">
-        <v>5</v>
-      </c>
-      <c r="E37" s="3">
-        <v>5</v>
-      </c>
-      <c r="F37" s="4">
+      <c r="D37" s="5">
+        <v>5</v>
+      </c>
+      <c r="E37" s="5">
+        <v>5</v>
+      </c>
+      <c r="F37" s="5">
         <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38" s="5">
         <v>36</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>123</v>
       </c>
-      <c r="D38" s="3">
-        <v>5</v>
-      </c>
-      <c r="E38" s="3">
-        <v>5</v>
-      </c>
-      <c r="F38" s="4">
+      <c r="D38" s="5">
+        <v>5</v>
+      </c>
+      <c r="E38" s="5">
+        <v>5</v>
+      </c>
+      <c r="F38" s="5">
         <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="5">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>104</v>
       </c>
-      <c r="D39" s="3">
-        <v>5</v>
-      </c>
-      <c r="E39" s="3">
-        <v>5</v>
-      </c>
-      <c r="F39" s="4">
+      <c r="D39" s="5">
+        <v>5</v>
+      </c>
+      <c r="E39" s="5">
+        <v>5</v>
+      </c>
+      <c r="F39" s="5">
         <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40" s="5">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>165</v>
       </c>
-      <c r="D40" s="3">
-        <v>5</v>
-      </c>
-      <c r="E40" s="3">
-        <v>5</v>
-      </c>
-      <c r="F40" s="4">
+      <c r="D40" s="5">
+        <v>5</v>
+      </c>
+      <c r="E40" s="5">
+        <v>5</v>
+      </c>
+      <c r="F40" s="5">
         <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41" s="5">
         <v>39</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>154</v>
       </c>
-      <c r="D41" s="3">
-        <v>5</v>
-      </c>
-      <c r="E41" s="3">
-        <v>5</v>
-      </c>
-      <c r="F41" s="4">
+      <c r="D41" s="5">
+        <v>5</v>
+      </c>
+      <c r="E41" s="5">
+        <v>5</v>
+      </c>
+      <c r="F41" s="5">
         <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="5">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>137</v>
       </c>
-      <c r="D42" s="3">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3">
-        <v>5</v>
-      </c>
-      <c r="F42" s="4">
+      <c r="D42" s="5">
+        <v>5</v>
+      </c>
+      <c r="E42" s="5">
+        <v>5</v>
+      </c>
+      <c r="F42" s="5">
         <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="5">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>141</v>
       </c>
-      <c r="D43" s="3">
-        <v>5</v>
-      </c>
-      <c r="E43" s="3">
-        <v>5</v>
-      </c>
-      <c r="F43" s="4">
+      <c r="D43" s="5">
+        <v>5</v>
+      </c>
+      <c r="E43" s="5">
+        <v>5</v>
+      </c>
+      <c r="F43" s="5">
         <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="5">
         <v>42</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>174</v>
       </c>
-      <c r="D44" s="3">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3">
-        <v>5</v>
-      </c>
-      <c r="F44" s="4">
+      <c r="D44" s="5">
+        <v>5</v>
+      </c>
+      <c r="E44" s="5">
+        <v>5</v>
+      </c>
+      <c r="F44" s="5">
         <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45" s="5">
         <v>43</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>154</v>
       </c>
-      <c r="D45" s="3">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="D45" s="5">
+        <v>5</v>
+      </c>
+      <c r="E45" s="5">
+        <v>5</v>
+      </c>
+      <c r="F45" s="5">
         <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46" s="5">
         <v>44</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>101</v>
       </c>
-      <c r="D46" s="3">
-        <v>5</v>
-      </c>
-      <c r="E46" s="3">
-        <v>5</v>
-      </c>
-      <c r="F46" s="4">
+      <c r="D46" s="5">
+        <v>5</v>
+      </c>
+      <c r="E46" s="5">
+        <v>5</v>
+      </c>
+      <c r="F46" s="5">
         <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="5">
         <v>45</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>146</v>
       </c>
-      <c r="D47" s="3">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
-        <v>5</v>
-      </c>
-      <c r="F47" s="4">
+      <c r="D47" s="5">
+        <v>5</v>
+      </c>
+      <c r="E47" s="5">
+        <v>5</v>
+      </c>
+      <c r="F47" s="5">
         <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48" s="5">
         <v>46</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="5">
         <v>167</v>
       </c>
-      <c r="D48" s="3">
-        <v>5</v>
-      </c>
-      <c r="E48" s="3">
-        <v>5</v>
-      </c>
-      <c r="F48" s="4">
+      <c r="D48" s="5">
+        <v>5</v>
+      </c>
+      <c r="E48" s="5">
+        <v>5</v>
+      </c>
+      <c r="F48" s="5">
         <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49" s="5">
         <v>47</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="5">
         <v>149</v>
       </c>
-      <c r="D49" s="3">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3">
-        <v>5</v>
-      </c>
-      <c r="F49" s="4">
+      <c r="D49" s="5">
+        <v>5</v>
+      </c>
+      <c r="E49" s="5">
+        <v>5</v>
+      </c>
+      <c r="F49" s="5">
         <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="5">
         <v>48</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="5">
         <v>130</v>
       </c>
-      <c r="D50" s="3">
-        <v>5</v>
-      </c>
-      <c r="E50" s="3">
-        <v>5</v>
-      </c>
-      <c r="F50" s="4">
+      <c r="D50" s="5">
+        <v>5</v>
+      </c>
+      <c r="E50" s="5">
+        <v>5</v>
+      </c>
+      <c r="F50" s="5">
         <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="A51" s="5">
         <v>49</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="5">
         <v>143</v>
       </c>
-      <c r="D51" s="3">
-        <v>5</v>
-      </c>
-      <c r="E51" s="3">
-        <v>5</v>
-      </c>
-      <c r="F51" s="4">
+      <c r="D51" s="5">
+        <v>5</v>
+      </c>
+      <c r="E51" s="5">
+        <v>5</v>
+      </c>
+      <c r="F51" s="5">
         <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="5">
+      <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="1">
         <v>161</v>
       </c>
-      <c r="D52" s="6">
-        <v>5</v>
-      </c>
-      <c r="E52" s="6">
-        <v>5</v>
-      </c>
-      <c r="F52" s="7">
+      <c r="D52" s="1">
+        <v>5</v>
+      </c>
+      <c r="E52" s="1">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1">
         <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="4">
         <v>7183</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="4">
         <v>250</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="4">
         <v>250</v>
       </c>
       <c r="F53" s="4">
